--- a/sensor_potencial_hidrico_ai/model/resultados_modelos_pure_alpha.xlsx
+++ b/sensor_potencial_hidrico_ai/model/resultados_modelos_pure_alpha.xlsx
@@ -461,38 +461,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'tanh', 'mlp__alpha': 0.001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 10000, 'mlp__solver': 'lbfgs'}</t>
+          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (15, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 10000, 'mlp__solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2341</v>
+        <v>0.5647</v>
       </c>
       <c r="D2" t="n">
-        <v>47.8594</v>
+        <v>31.0471</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.22      0.63      0.33        99
-           1       0.20      0.05      0.08       104
-           2       0.20      0.15      0.17       112
-           3       0.16      0.56      0.25        86
-           4       0.13      0.09      0.11        88
-           5       0.08      0.09      0.08        98
-           6       0.53      0.43      0.47       101
-           7       0.17      0.02      0.04        94
-           8       0.00      0.00      0.00        99
-           9       0.36      1.00      0.53       105
-          10       0.49      0.18      0.27       121
-          11       0.14      0.03      0.05        99
-          12       0.12      0.10      0.11        94
-          13       0.74      0.32      0.45        97
-          14       0.00      0.00      0.00       102
-          15       0.11      0.15      0.13        91
-          16       0.14      0.18      0.16       110
-    accuracy                           0.23      1700
-   macro avg       0.22      0.23      0.19      1700
-weighted avg       0.23      0.23      0.19      1700
+           0       0.75      0.99      0.86        99
+           1       0.21      0.15      0.18       104
+           2       0.35      0.38      0.36       112
+           3       0.72      0.67      0.70        86
+           4       0.34      0.48      0.40        88
+           5       0.51      0.47      0.49        98
+           6       0.92      0.97      0.95       101
+           7       0.48      0.67      0.56        94
+           8       0.38      0.21      0.27        99
+           9       0.98      1.00      0.99       105
+          10       0.95      0.94      0.95       121
+          11       0.34      0.25      0.29        99
+          12       0.27      0.21      0.24        94
+          13       0.94      1.00      0.97        97
+          14       0.25      0.29      0.27       102
+          15       0.17      0.09      0.12        91
+          16       0.55      0.69      0.62       110
+    accuracy                           0.56      1700
+   macro avg       0.54      0.56      0.54      1700
+weighted avg       0.54      0.56      0.55      1700
 </t>
         </is>
       </c>
@@ -506,38 +506,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'scv__C': 10, 'scv__gamma': 0.001, 'scv__kernel': 'rbf', 'scv__random_state': 42}</t>
+          <t>{'scv__C': 10, 'scv__gamma': 0.1, 'scv__kernel': 'rbf', 'scv__random_state': 42}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2776</v>
+        <v>0.7582</v>
       </c>
       <c r="D3" t="n">
-        <v>33.5447</v>
+        <v>20.2482</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.44      0.39      0.41        99
-           1       0.23      0.10      0.14       104
-           2       0.41      0.16      0.23       112
-           3       0.26      0.15      0.19        86
-           4       0.25      0.15      0.19        88
-           5       0.34      0.14      0.20        98
-           6       0.81      0.39      0.52       101
-           7       0.12      0.07      0.09        94
-           8       0.31      0.18      0.23        99
-           9       0.98      1.00      0.99       105
-          10       0.13      0.86      0.22       121
-          11       0.21      0.10      0.14        99
-          12       0.29      0.19      0.23        94
-          13       0.79      0.31      0.44        97
-          14       0.20      0.08      0.11       102
-          15       0.24      0.10      0.14        91
-          16       0.27      0.15      0.20       110
-    accuracy                           0.28      1700
-   macro avg       0.37      0.27      0.28      1700
-weighted avg       0.37      0.28      0.28      1700
+           0       0.82      0.99      0.90        99
+           1       0.53      0.52      0.52       104
+           2       0.56      0.59      0.58       112
+           3       0.89      0.97      0.93        86
+           4       0.56      0.56      0.56        88
+           5       0.86      0.70      0.78        98
+           6       0.95      0.98      0.97       101
+           7       0.88      0.68      0.77        94
+           8       0.94      0.77      0.84        99
+           9       0.95      1.00      0.97       105
+          10       0.93      0.96      0.94       121
+          11       0.47      0.52      0.49        99
+          12       0.90      0.60      0.72        94
+          13       0.90      1.00      0.95        97
+          14       0.43      0.47      0.45       102
+          15       0.81      0.55      0.65        91
+          16       0.69      0.98      0.81       110
+    accuracy                           0.76      1700
+   macro avg       0.77      0.75      0.75      1700
+weighted avg       0.77      0.76      0.76      1700
 </t>
         </is>
       </c>

--- a/sensor_potencial_hidrico_ai/model/resultados_modelos_pure_alpha.xlsx
+++ b/sensor_potencial_hidrico_ai/model/resultados_modelos_pure_alpha.xlsx
@@ -461,38 +461,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'relu', 'mlp__alpha': 0.0001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (15, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 10000, 'mlp__solver': 'lbfgs'}</t>
+          <t>{'mlp__activation': 'tanh', 'mlp__alpha': 0.001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 10000, 'mlp__solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5647</v>
+        <v>0.2341</v>
       </c>
       <c r="D2" t="n">
-        <v>31.0471</v>
+        <v>47.8594</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.75      0.99      0.86        99
-           1       0.21      0.15      0.18       104
-           2       0.35      0.38      0.36       112
-           3       0.72      0.67      0.70        86
-           4       0.34      0.48      0.40        88
-           5       0.51      0.47      0.49        98
-           6       0.92      0.97      0.95       101
-           7       0.48      0.67      0.56        94
-           8       0.38      0.21      0.27        99
-           9       0.98      1.00      0.99       105
-          10       0.95      0.94      0.95       121
-          11       0.34      0.25      0.29        99
-          12       0.27      0.21      0.24        94
-          13       0.94      1.00      0.97        97
-          14       0.25      0.29      0.27       102
-          15       0.17      0.09      0.12        91
-          16       0.55      0.69      0.62       110
-    accuracy                           0.56      1700
-   macro avg       0.54      0.56      0.54      1700
-weighted avg       0.54      0.56      0.55      1700
+           0       0.22      0.63      0.33        99
+           1       0.20      0.05      0.08       104
+           2       0.20      0.15      0.17       112
+           3       0.16      0.56      0.25        86
+           4       0.13      0.09      0.11        88
+           5       0.08      0.09      0.08        98
+           6       0.53      0.43      0.47       101
+           7       0.17      0.02      0.04        94
+           8       0.00      0.00      0.00        99
+           9       0.36      1.00      0.53       105
+          10       0.49      0.18      0.27       121
+          11       0.14      0.03      0.05        99
+          12       0.12      0.10      0.11        94
+          13       0.74      0.32      0.45        97
+          14       0.00      0.00      0.00       102
+          15       0.11      0.15      0.13        91
+          16       0.14      0.18      0.16       110
+    accuracy                           0.23      1700
+   macro avg       0.22      0.23      0.19      1700
+weighted avg       0.23      0.23      0.19      1700
 </t>
         </is>
       </c>
@@ -506,38 +506,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'scv__C': 10, 'scv__gamma': 0.1, 'scv__kernel': 'rbf', 'scv__random_state': 42}</t>
+          <t>{'scv__C': 10, 'scv__gamma': 0.001, 'scv__kernel': 'rbf', 'scv__random_state': 42}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.7582</v>
+        <v>0.2776</v>
       </c>
       <c r="D3" t="n">
-        <v>20.2482</v>
+        <v>33.5447</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.82      0.99      0.90        99
-           1       0.53      0.52      0.52       104
-           2       0.56      0.59      0.58       112
-           3       0.89      0.97      0.93        86
-           4       0.56      0.56      0.56        88
-           5       0.86      0.70      0.78        98
-           6       0.95      0.98      0.97       101
-           7       0.88      0.68      0.77        94
-           8       0.94      0.77      0.84        99
-           9       0.95      1.00      0.97       105
-          10       0.93      0.96      0.94       121
-          11       0.47      0.52      0.49        99
-          12       0.90      0.60      0.72        94
-          13       0.90      1.00      0.95        97
-          14       0.43      0.47      0.45       102
-          15       0.81      0.55      0.65        91
-          16       0.69      0.98      0.81       110
-    accuracy                           0.76      1700
-   macro avg       0.77      0.75      0.75      1700
-weighted avg       0.77      0.76      0.76      1700
+           0       0.44      0.39      0.41        99
+           1       0.23      0.10      0.14       104
+           2       0.41      0.16      0.23       112
+           3       0.26      0.15      0.19        86
+           4       0.25      0.15      0.19        88
+           5       0.34      0.14      0.20        98
+           6       0.81      0.39      0.52       101
+           7       0.12      0.07      0.09        94
+           8       0.31      0.18      0.23        99
+           9       0.98      1.00      0.99       105
+          10       0.13      0.86      0.22       121
+          11       0.21      0.10      0.14        99
+          12       0.29      0.19      0.23        94
+          13       0.79      0.31      0.44        97
+          14       0.20      0.08      0.11       102
+          15       0.24      0.10      0.14        91
+          16       0.27      0.15      0.20       110
+    accuracy                           0.28      1700
+   macro avg       0.37      0.27      0.28      1700
+weighted avg       0.37      0.28      0.28      1700
 </t>
         </is>
       </c>

--- a/sensor_potencial_hidrico_ai/model/resultados_modelos_pure_alpha.xlsx
+++ b/sensor_potencial_hidrico_ai/model/resultados_modelos_pure_alpha.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,15 +441,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>roc_auc_score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>mse</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>relatorio_classificacao</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>n_combinations</t>
         </is>
@@ -461,43 +466,46 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'mlp__activation': 'tanh', 'mlp__alpha': 0.001, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 10000, 'mlp__solver': 'lbfgs'}</t>
+          <t>{'mlp__activation': 'tanh', 'mlp__alpha': 0.01, 'mlp__early_stopping': True, 'mlp__hidden_layer_sizes': (20, 10), 'mlp__learning_rate': 'constant', 'mlp__learning_rate_init': 0.001, 'mlp__max_iter': 5000, 'mlp__solver': 'adam'}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2341</v>
+        <v>0.1659</v>
       </c>
       <c r="D2" t="n">
-        <v>47.8594</v>
-      </c>
-      <c r="E2" t="inlineStr">
+        <v>0.6621</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42.8894</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
-           0       0.22      0.63      0.33        99
-           1       0.20      0.05      0.08       104
-           2       0.20      0.15      0.17       112
-           3       0.16      0.56      0.25        86
-           4       0.13      0.09      0.11        88
-           5       0.08      0.09      0.08        98
-           6       0.53      0.43      0.47       101
-           7       0.17      0.02      0.04        94
-           8       0.00      0.00      0.00        99
-           9       0.36      1.00      0.53       105
-          10       0.49      0.18      0.27       121
-          11       0.14      0.03      0.05        99
-          12       0.12      0.10      0.11        94
-          13       0.74      0.32      0.45        97
-          14       0.00      0.00      0.00       102
-          15       0.11      0.15      0.13        91
-          16       0.14      0.18      0.16       110
-    accuracy                           0.23      1700
-   macro avg       0.22      0.23      0.19      1700
-weighted avg       0.23      0.23      0.19      1700
+           0       0.05      0.04      0.05        99
+           1       0.12      0.10      0.11       104
+           2       0.05      0.01      0.01       112
+           3       0.12      0.16      0.14        86
+           4       0.10      0.23      0.14        88
+           5       0.21      0.05      0.08        98
+           6       0.25      0.30      0.27       101
+           7       0.07      0.10      0.08        94
+           8       0.02      0.01      0.01        99
+           9       0.34      1.00      0.51       105
+          10       0.38      0.05      0.09       121
+          11       0.14      0.05      0.07        99
+          12       0.06      0.10      0.08        94
+          13       0.25      0.42      0.32        97
+          14       0.07      0.02      0.03       102
+          15       0.07      0.02      0.03        91
+          16       0.12      0.16      0.14       110
+    accuracy                           0.17      1700
+   macro avg       0.14      0.17      0.13      1700
+weighted avg       0.15      0.17      0.13      1700
 </t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>72</v>
+      <c r="G2" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="3">
@@ -506,16 +514,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'scv__C': 10, 'scv__gamma': 0.001, 'scv__kernel': 'rbf', 'scv__random_state': 42}</t>
+          <t>{'svc__C': 10, 'svc__gamma': 0.001, 'svc__kernel': 'rbf', 'svc__probability': True, 'svc__random_state': 42}</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0.2776</v>
       </c>
       <c r="D3" t="n">
+        <v>0.7564</v>
+      </c>
+      <c r="E3" t="n">
         <v>33.5447</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">              precision    recall  f1-score   support
            0       0.44      0.39      0.41        99
@@ -541,7 +552,7 @@
 </t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>9</v>
       </c>
     </row>
